--- a/files/STable-5.xlsx
+++ b/files/STable-5.xlsx
@@ -43,16 +43,16 @@
     <t>YP</t>
   </si>
   <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>SWd</t>
+  </si>
+  <si>
     <t>D90M</t>
   </si>
   <si>
     <t>PW</t>
-  </si>
-  <si>
-    <t>SW</t>
-  </si>
-  <si>
-    <t>SWd</t>
   </si>
   <si>
     <t>D50F</t>
@@ -462,19 +462,19 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>0.8433897962320118</v>
+        <v>0.841240033654277</v>
       </c>
       <c r="D2">
-        <v>3.376441992663671E-22</v>
+        <v>5.435846943391555E-22</v>
       </c>
       <c r="E2">
-        <v>4.591961110022592E-20</v>
+        <v>7.392751843012515E-20</v>
       </c>
       <c r="F2">
-        <v>0.7314578606246662</v>
+        <v>0.7327080856473819</v>
       </c>
       <c r="G2">
-        <v>0.9046974664455223</v>
+        <v>0.9067674597948551</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -485,19 +485,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.7294318529814402</v>
+        <v>0.7303203125987935</v>
       </c>
       <c r="D3">
-        <v>3.624058791860473E-14</v>
+        <v>3.257514370225783E-14</v>
       </c>
       <c r="E3">
-        <v>2.464359978465121E-12</v>
+        <v>2.215109771753533E-12</v>
       </c>
       <c r="F3">
-        <v>0.5678935596561318</v>
+        <v>0.6061724773436278</v>
       </c>
       <c r="G3">
-        <v>0.8434800226073584</v>
+        <v>0.8139967158647793</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -508,19 +508,19 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>0.7212660756964553</v>
+        <v>0.7268645887532209</v>
       </c>
       <c r="D4">
-        <v>9.472220513919731E-14</v>
+        <v>4.920290070843826E-14</v>
       </c>
       <c r="E4">
-        <v>4.294073299643612E-12</v>
+        <v>2.230531498782534E-12</v>
       </c>
       <c r="F4">
-        <v>0.5848475680769235</v>
+        <v>0.56549299939911</v>
       </c>
       <c r="G4">
-        <v>0.8080806005670755</v>
+        <v>0.844468878272855</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -528,22 +528,22 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>0.7077934830578776</v>
+        <v>0.7105630932351191</v>
       </c>
       <c r="D5">
-        <v>4.301041720151525E-13</v>
+        <v>3.17346627602201E-13</v>
       </c>
       <c r="E5">
-        <v>1.462354184851519E-11</v>
+        <v>1.078978533847484E-11</v>
       </c>
       <c r="F5">
-        <v>0.5308230448049045</v>
+        <v>0.5387676402060773</v>
       </c>
       <c r="G5">
-        <v>0.8181892459973736</v>
+        <v>0.8231176760513036</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -551,22 +551,22 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>0.6870471300851047</v>
+        <v>0.677107702424158</v>
       </c>
       <c r="D6">
-        <v>3.768145726306644E-12</v>
+        <v>1.001393355611184E-11</v>
       </c>
       <c r="E6">
-        <v>1.024935637555407E-10</v>
+        <v>2.723789927262421E-10</v>
       </c>
       <c r="F6">
-        <v>0.522333968234778</v>
+        <v>0.5062875473002136</v>
       </c>
       <c r="G6">
-        <v>0.8050840730681147</v>
+        <v>0.8020049822611088</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -574,22 +574,22 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>0.6689683540892409</v>
+        <v>0.6680325040750132</v>
       </c>
       <c r="D7">
-        <v>2.168407339162699E-11</v>
+        <v>2.366190640204304E-11</v>
       </c>
       <c r="E7">
-        <v>4.915056635435452E-10</v>
+        <v>5.363365451129757E-10</v>
       </c>
       <c r="F7">
-        <v>0.4886278687577096</v>
+        <v>0.4878062862656798</v>
       </c>
       <c r="G7">
-        <v>0.8021925203724906</v>
+        <v>0.7991860933950174</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -600,19 +600,19 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>0.6221247107323056</v>
+        <v>0.6194438472919485</v>
       </c>
       <c r="D8">
-        <v>1.202959264420291E-09</v>
+        <v>1.483833069698572E-09</v>
       </c>
       <c r="E8">
-        <v>2.337177999445137E-08</v>
+        <v>2.882875678271512E-08</v>
       </c>
       <c r="F8">
-        <v>0.4252660404638354</v>
+        <v>0.4191700703578853</v>
       </c>
       <c r="G8">
-        <v>0.7706712293277842</v>
+        <v>0.7740910127407445</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -623,19 +623,19 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>0.6009471601124189</v>
+        <v>0.6001884203791007</v>
       </c>
       <c r="D9">
-        <v>5.989515225201062E-09</v>
+        <v>6.330389059501305E-09</v>
       </c>
       <c r="E9">
-        <v>1.018217588284181E-07</v>
+        <v>1.076166140115222E-07</v>
       </c>
       <c r="F9">
-        <v>0.4079587152111419</v>
+        <v>0.4169240530751535</v>
       </c>
       <c r="G9">
-        <v>0.7485805108302619</v>
+        <v>0.7434006271517746</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -643,22 +643,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>0.5817482817233602</v>
+        <v>0.581697694916254</v>
       </c>
       <c r="D10">
-        <v>2.327738582407682E-08</v>
+        <v>2.335809992451966E-08</v>
       </c>
       <c r="E10">
-        <v>3.517471635638275E-07</v>
+        <v>3.529668433038526E-07</v>
       </c>
       <c r="F10">
-        <v>0.3788771363938357</v>
+        <v>0.3852655945823297</v>
       </c>
       <c r="G10">
-        <v>0.7390586078883447</v>
+        <v>0.7378556736574011</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -666,22 +666,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>0.5739360256062928</v>
+        <v>0.5735313644151897</v>
       </c>
       <c r="D11">
-        <v>3.945485488748267E-08</v>
+        <v>4.053299262809841E-08</v>
       </c>
       <c r="E11">
-        <v>5.365860264697643E-07</v>
+        <v>5.512486997421384E-07</v>
       </c>
       <c r="F11">
-        <v>0.3829915873714618</v>
+        <v>0.3964554976136651</v>
       </c>
       <c r="G11">
-        <v>0.7218507073799055</v>
+        <v>0.7167629500703024</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -692,180 +692,180 @@
         <v>16</v>
       </c>
       <c r="C12">
-        <v>0.5678327358903337</v>
+        <v>0.5664224444351331</v>
       </c>
       <c r="D12">
-        <v>5.902375674397245E-08</v>
+        <v>6.470619829697908E-08</v>
       </c>
       <c r="E12">
-        <v>7.297482651982048E-07</v>
+        <v>8.000039062171959E-07</v>
       </c>
       <c r="F12">
-        <v>0.3698462038021173</v>
+        <v>0.3754118901716936</v>
       </c>
       <c r="G12">
-        <v>0.719382128307674</v>
+        <v>0.707190554146107</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>0.5622858154503723</v>
+        <v>0.5549766689007194</v>
       </c>
       <c r="D13">
-        <v>8.452159640415208E-08</v>
+        <v>1.343221883753446E-07</v>
       </c>
       <c r="E13">
-        <v>9.579114259137237E-07</v>
+        <v>1.522318134920573E-06</v>
       </c>
       <c r="F13">
-        <v>0.3705564055761668</v>
+        <v>0.3453613108317161</v>
       </c>
       <c r="G13">
-        <v>0.7330077125839248</v>
+        <v>0.7003429200781897</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>0.5560641889755812</v>
+        <v>0.5419011368378456</v>
       </c>
       <c r="D14">
-        <v>1.254639922333561E-07</v>
+        <v>2.9941335568494E-07</v>
       </c>
       <c r="E14">
-        <v>1.312546380287418E-06</v>
+        <v>3.132324336396295E-06</v>
       </c>
       <c r="F14">
-        <v>0.3536133468622491</v>
+        <v>0.3325934907997521</v>
       </c>
       <c r="G14">
-        <v>0.707037038426413</v>
+        <v>0.707646421870801</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>0.5295084662173268</v>
+        <v>0.5340861669975593</v>
       </c>
       <c r="D15">
-        <v>6.206934258799987E-07</v>
+        <v>4.757697978560951E-07</v>
       </c>
       <c r="E15">
-        <v>6.02959327997713E-06</v>
+        <v>4.621763750602066E-06</v>
       </c>
       <c r="F15">
-        <v>0.3472014637208257</v>
+        <v>0.3250976033651428</v>
       </c>
       <c r="G15">
-        <v>0.682716816341549</v>
+        <v>0.6962854413484242</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>0.5260941590055513</v>
+        <v>0.5211605280359612</v>
       </c>
       <c r="D16">
-        <v>7.549364852253834E-07</v>
+        <v>9.980489188121695E-07</v>
       </c>
       <c r="E16">
-        <v>6.844757466043475E-06</v>
+        <v>9.048976863897003E-06</v>
       </c>
       <c r="F16">
-        <v>0.3162779636040072</v>
+        <v>0.3235957839273667</v>
       </c>
       <c r="G16">
-        <v>0.6916823891888583</v>
+        <v>0.6867549216239675</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C17">
-        <v>0.5165637235324674</v>
+        <v>0.5119816891968789</v>
       </c>
       <c r="D17">
-        <v>1.289465474688055E-06</v>
+        <v>1.658444509402027E-06</v>
       </c>
       <c r="E17">
-        <v>1.096045653484847E-05</v>
+        <v>1.409677832991723E-05</v>
       </c>
       <c r="F17">
-        <v>0.3130400599215978</v>
+        <v>0.3192762242186512</v>
       </c>
       <c r="G17">
-        <v>0.6863011676654948</v>
+        <v>0.6623580930480807</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C18">
-        <v>0.5024500970655009</v>
+        <v>-0.5032309462689208</v>
       </c>
       <c r="D18">
-        <v>2.767069921048175E-06</v>
+        <v>2.654963638275848E-06</v>
       </c>
       <c r="E18">
-        <v>2.21365593683854E-05</v>
+        <v>2.123970910620679E-05</v>
       </c>
       <c r="F18">
-        <v>0.3230407792494042</v>
+        <v>-0.6826718301350008</v>
       </c>
       <c r="G18">
-        <v>0.6523530820840054</v>
+        <v>-0.2888564646871137</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
       </c>
       <c r="C19">
-        <v>0.4955329198300839</v>
+        <v>0.497543580123377</v>
       </c>
       <c r="D19">
-        <v>3.973865028408505E-06</v>
+        <v>3.579926667872724E-06</v>
       </c>
       <c r="E19">
-        <v>3.002475799241982E-05</v>
+        <v>2.704833482392725E-05</v>
       </c>
       <c r="F19">
-        <v>0.2895697776672201</v>
+        <v>0.3037017556677144</v>
       </c>
       <c r="G19">
-        <v>0.6649584537411698</v>
+        <v>0.645002156498521</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -873,68 +873,68 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>-0.4931650627853159</v>
+        <v>0.4946983061234339</v>
       </c>
       <c r="D20">
-        <v>4.489928298744918E-06</v>
+        <v>4.14905127856661E-06</v>
       </c>
       <c r="E20">
-        <v>3.213843413838468E-05</v>
+        <v>2.969847230973995E-05</v>
       </c>
       <c r="F20">
-        <v>-0.672961950291051</v>
+        <v>0.2869792158235577</v>
       </c>
       <c r="G20">
-        <v>-0.2776751460228291</v>
+        <v>0.6588004313206942</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C21">
-        <v>0.4792563802591049</v>
+        <v>0.4756713701933687</v>
       </c>
       <c r="D21">
-        <v>9.03366723327288E-06</v>
+        <v>1.076463216621965E-05</v>
       </c>
       <c r="E21">
-        <v>6.142893718625558E-05</v>
+        <v>7.31994987302936E-05</v>
       </c>
       <c r="F21">
-        <v>0.2941363098115815</v>
+        <v>0.267212551468998</v>
       </c>
       <c r="G21">
-        <v>0.6371935437345678</v>
+        <v>0.6460243518300548</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>0.4780236121005808</v>
+        <v>0.4744886038352692</v>
       </c>
       <c r="D22">
-        <v>9.597122559651123E-06</v>
+        <v>1.140067677998734E-05</v>
       </c>
       <c r="E22">
-        <v>6.215279371964537E-05</v>
+        <v>7.383295438467992E-05</v>
       </c>
       <c r="F22">
-        <v>0.2649498925009302</v>
+        <v>0.2780058711882905</v>
       </c>
       <c r="G22">
-        <v>0.6496164316309823</v>
+        <v>0.6233976780264899</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -945,19 +945,19 @@
         <v>21</v>
       </c>
       <c r="C23">
-        <v>0.4748643627502491</v>
+        <v>0.4725120464758391</v>
       </c>
       <c r="D23">
-        <v>1.119489564084202E-05</v>
+        <v>1.254263438785597E-05</v>
       </c>
       <c r="E23">
-        <v>6.92048094161143E-05</v>
+        <v>7.753628530674596E-05</v>
       </c>
       <c r="F23">
-        <v>0.2573582472314725</v>
+        <v>0.2567411274259113</v>
       </c>
       <c r="G23">
-        <v>0.6450602689262662</v>
+        <v>0.6357274609886922</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -968,272 +968,272 @@
         <v>20</v>
       </c>
       <c r="C24">
-        <v>-0.4602359665650804</v>
+        <v>-0.4589461171739652</v>
       </c>
       <c r="D24">
-        <v>2.239837378301222E-05</v>
+        <v>2.37749393330731E-05</v>
       </c>
       <c r="E24">
-        <v>0.0001324425580212897</v>
+        <v>0.0001405822499694757</v>
       </c>
       <c r="F24">
-        <v>-0.6467982909878802</v>
+        <v>-0.6432546004419195</v>
       </c>
       <c r="G24">
-        <v>-0.2333559617247687</v>
+        <v>-0.2342906097989537</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25">
-        <v>0.4515358059661856</v>
+        <v>0.4441002035938744</v>
       </c>
       <c r="D25">
-        <v>3.333723422671566E-05</v>
+        <v>4.643727407844156E-05</v>
       </c>
       <c r="E25">
-        <v>0.0001889109939513887</v>
+        <v>0.0002591706205350206</v>
       </c>
       <c r="F25">
-        <v>0.2366405359184631</v>
+        <v>0.2274277428879549</v>
       </c>
       <c r="G25">
-        <v>0.6373088996505876</v>
+        <v>0.629827061329479</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26">
-        <v>0.4441002035938744</v>
+        <v>0.443518506809646</v>
       </c>
       <c r="D26">
-        <v>4.643727407844156E-05</v>
+        <v>4.764165818658468E-05</v>
       </c>
       <c r="E26">
-        <v>0.0002526187709867221</v>
+        <v>0.0002591706205350206</v>
       </c>
       <c r="F26">
-        <v>0.2375080573754331</v>
+        <v>0.2345251550700495</v>
       </c>
       <c r="G26">
-        <v>0.6226025056947607</v>
+        <v>0.6189642642225928</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>0.4419897190374745</v>
+        <v>-0.4321213908638559</v>
       </c>
       <c r="D27">
-        <v>5.09467237277045E-05</v>
+        <v>7.795413615323767E-05</v>
       </c>
       <c r="E27">
-        <v>0.0002664905548833774</v>
+        <v>0.0003926578709940861</v>
       </c>
       <c r="F27">
-        <v>0.2410922090804842</v>
+        <v>-0.622887876876831</v>
       </c>
       <c r="G27">
-        <v>0.5999472380464853</v>
+        <v>-0.2087176909518784</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28">
-        <v>0.4333997295619466</v>
+        <v>0.4321477140023717</v>
       </c>
       <c r="D28">
-        <v>7.382948138990052E-05</v>
+        <v>7.786709214678512E-05</v>
       </c>
       <c r="E28">
-        <v>0.0003718818321861656</v>
+        <v>0.0003926578709940861</v>
       </c>
       <c r="F28">
-        <v>0.210421565544144</v>
+        <v>0.2024131553945278</v>
       </c>
       <c r="G28">
-        <v>0.6160625682443555</v>
+        <v>0.6140516423579772</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C29">
-        <v>-0.4284712396555513</v>
+        <v>0.4301277878636268</v>
       </c>
       <c r="D29">
-        <v>9.093615326370678E-05</v>
+        <v>8.481467617710102E-05</v>
       </c>
       <c r="E29">
-        <v>0.0004416898872808615</v>
+        <v>0.0004119569985744907</v>
       </c>
       <c r="F29">
-        <v>-0.6086675236818193</v>
+        <v>0.2399049716468087</v>
       </c>
       <c r="G29">
-        <v>-0.2135326146557469</v>
+        <v>0.6033166342865806</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C30">
-        <v>0.4194919005045586</v>
+        <v>0.4155716038629008</v>
       </c>
       <c r="D30">
-        <v>0.0001318540202905579</v>
+        <v>0.0001545724352177218</v>
       </c>
       <c r="E30">
-        <v>0.000618349888259168</v>
+        <v>0.0006822937616846622</v>
       </c>
       <c r="F30">
-        <v>0.2169143517903002</v>
+        <v>0.1700616244308008</v>
       </c>
       <c r="G30">
-        <v>0.6083852326656158</v>
+        <v>0.615844993378225</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C31">
-        <v>0.416153466786378</v>
+        <v>-0.4154194697502374</v>
       </c>
       <c r="D31">
-        <v>0.0001509866498117429</v>
+        <v>0.0001555228427369451</v>
       </c>
       <c r="E31">
-        <v>0.000673970158635561</v>
+        <v>0.0006822937616846622</v>
       </c>
       <c r="F31">
-        <v>0.1876909001628149</v>
+        <v>-0.6147019362692845</v>
       </c>
       <c r="G31">
-        <v>0.593172591544526</v>
+        <v>-0.1901076855501431</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C32">
-        <v>-0.4154956298993988</v>
+        <v>-0.4155553461825504</v>
       </c>
       <c r="D32">
-        <v>0.0001550463857548262</v>
+        <v>0.0001546737434443467</v>
       </c>
       <c r="E32">
-        <v>0.000673970158635561</v>
+        <v>0.0006822937616846622</v>
       </c>
       <c r="F32">
-        <v>-0.6055837737592425</v>
+        <v>-0.6107474812750212</v>
       </c>
       <c r="G32">
-        <v>-0.1830318347448562</v>
+        <v>-0.1780052580097413</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>-0.4149356617136699</v>
+        <v>0.4097295109953337</v>
       </c>
       <c r="D33">
-        <v>0.0001585812137966026</v>
+        <v>0.0001951890276723984</v>
       </c>
       <c r="E33">
-        <v>0.000673970158635561</v>
+        <v>0.0008069700019443538</v>
       </c>
       <c r="F33">
-        <v>-0.6037137609581759</v>
+        <v>0.1915688423333978</v>
       </c>
       <c r="G33">
-        <v>-0.1758688210429369</v>
+        <v>0.601603758574192</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
       <c r="C34">
-        <v>0.4132571110907628</v>
+        <v>0.4096493737954647</v>
       </c>
       <c r="D34">
-        <v>0.000169627290051696</v>
+        <v>0.0001958088975306153</v>
       </c>
       <c r="E34">
-        <v>0.0006990700438494138</v>
+        <v>0.0008069700019443538</v>
       </c>
       <c r="F34">
-        <v>0.1841062148163921</v>
+        <v>0.1691183445629206</v>
       </c>
       <c r="G34">
-        <v>0.6073693373544636</v>
+        <v>0.5934433982312256</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C35">
-        <v>0.4090802758138397</v>
+        <v>0.4064669507707481</v>
       </c>
       <c r="D35">
-        <v>0.0002002633425271513</v>
+        <v>0.0002219413571623901</v>
       </c>
       <c r="E35">
-        <v>0.0008010533701086051</v>
+        <v>0.0008877654286495604</v>
       </c>
       <c r="F35">
-        <v>0.1726936118811304</v>
+        <v>0.1919925863298362</v>
       </c>
       <c r="G35">
-        <v>0.5957975657963867</v>
+        <v>0.5876571044908357</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1244,19 +1244,19 @@
         <v>22</v>
       </c>
       <c r="C36">
-        <v>0.401724912153113</v>
+        <v>0.4036091634803021</v>
       </c>
       <c r="D36">
-        <v>0.0002668736721202717</v>
+        <v>0.0002481038490298298</v>
       </c>
       <c r="E36">
-        <v>0.00103699484023877</v>
+        <v>0.00096406067051591</v>
       </c>
       <c r="F36">
-        <v>0.1660382335804385</v>
+        <v>0.1681566620843229</v>
       </c>
       <c r="G36">
-        <v>0.5992648889089138</v>
+        <v>0.6035204147900253</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1267,157 +1267,157 @@
         <v>14</v>
       </c>
       <c r="C37">
-        <v>0.3976656255137267</v>
+        <v>0.401408717864414</v>
       </c>
       <c r="D37">
-        <v>0.0003118201651262063</v>
+        <v>0.0002701483224410239</v>
       </c>
       <c r="E37">
-        <v>0.001177987290476779</v>
+        <v>0.001020560329221646</v>
       </c>
       <c r="F37">
-        <v>0.1848968604434676</v>
+        <v>0.1865696131477103</v>
       </c>
       <c r="G37">
-        <v>0.5775063320220306</v>
+        <v>0.5767190838673124</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C38">
-        <v>0.3841095613247511</v>
+        <v>0.3898506556734404</v>
       </c>
       <c r="D38">
-        <v>0.0005169999363224758</v>
+        <v>0.0004184453913180441</v>
       </c>
       <c r="E38">
-        <v>0.001900324090266398</v>
+        <v>0.001538069546466324</v>
       </c>
       <c r="F38">
-        <v>0.1622956177990181</v>
+        <v>0.1670537885054541</v>
       </c>
       <c r="G38">
-        <v>0.5762872902087104</v>
+        <v>0.5618360115201501</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39">
-        <v>-0.3830368991862969</v>
+        <v>-0.387214371347067</v>
       </c>
       <c r="D39">
-        <v>0.0005376108198302141</v>
+        <v>0.0004613425507970313</v>
       </c>
       <c r="E39">
-        <v>0.00192408082886603</v>
+        <v>0.001651120708115691</v>
       </c>
       <c r="F39">
-        <v>-0.5929334779584243</v>
+        <v>-0.5910816295354712</v>
       </c>
       <c r="G39">
-        <v>-0.1382638786418282</v>
+        <v>-0.1382464561232271</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C40">
-        <v>0.3816816095297107</v>
+        <v>0.381656318365179</v>
       </c>
       <c r="D40">
-        <v>0.0005647244073424799</v>
+        <v>0.0005652420307548867</v>
       </c>
       <c r="E40">
-        <v>0.001969295369194289</v>
+        <v>0.001971100414940118</v>
       </c>
       <c r="F40">
-        <v>0.1472033979405063</v>
+        <v>0.170946428705502</v>
       </c>
       <c r="G40">
-        <v>0.5727552374698001</v>
+        <v>0.5726626854155867</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C41">
-        <v>0.3801135573287471</v>
+        <v>-0.3792869187379724</v>
       </c>
       <c r="D41">
-        <v>0.0005976481247780375</v>
+        <v>0.0006157007747440961</v>
       </c>
       <c r="E41">
-        <v>0.002032003624245327</v>
+        <v>0.002070946904538634</v>
       </c>
       <c r="F41">
-        <v>0.1672758515796413</v>
+        <v>-0.5737244878725456</v>
       </c>
       <c r="G41">
-        <v>0.5546369880260335</v>
+        <v>-0.1337811864675235</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C42">
-        <v>0.367215063417595</v>
+        <v>0.3788995814312269</v>
       </c>
       <c r="D42">
-        <v>0.000942526104154137</v>
+        <v>0.0006243295815153235</v>
       </c>
       <c r="E42">
-        <v>0.003126428052803967</v>
+        <v>0.002070946904538634</v>
       </c>
       <c r="F42">
-        <v>0.1578486140489183</v>
+        <v>0.1578697001814182</v>
       </c>
       <c r="G42">
-        <v>0.5513610803446862</v>
+        <v>0.5706506227136343</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C43">
-        <v>-0.3632987260428481</v>
+        <v>0.3617646881597189</v>
       </c>
       <c r="D43">
-        <v>0.001078387185792705</v>
+        <v>0.00113627443194448</v>
       </c>
       <c r="E43">
-        <v>0.003491920411138284</v>
+        <v>0.003679364827248791</v>
       </c>
       <c r="F43">
-        <v>-0.5612293271099126</v>
+        <v>0.1188114850379105</v>
       </c>
       <c r="G43">
-        <v>-0.1052197637698844</v>
+        <v>0.5656167138889565</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1428,65 +1428,65 @@
         <v>7</v>
       </c>
       <c r="C44">
-        <v>0.3623349690065787</v>
+        <v>0.3559234155622699</v>
       </c>
       <c r="D44">
-        <v>0.001114433913767433</v>
+        <v>0.001383368916998972</v>
       </c>
       <c r="E44">
-        <v>0.003524721215636533</v>
+        <v>0.004375306342136284</v>
       </c>
       <c r="F44">
-        <v>0.1401192625218262</v>
+        <v>0.1162798548112041</v>
       </c>
       <c r="G44">
-        <v>0.5576863339211803</v>
+        <v>0.5599447329909532</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C45">
-        <v>0.357073306440395</v>
+        <v>-0.350775806472009</v>
       </c>
       <c r="D45">
-        <v>0.001331196062391756</v>
+        <v>0.001640315511433057</v>
       </c>
       <c r="E45">
-        <v>0.004071205487447212</v>
+        <v>0.005070066126247631</v>
       </c>
       <c r="F45">
-        <v>0.1243943113821331</v>
+        <v>-0.5497711568023922</v>
       </c>
       <c r="G45">
-        <v>0.5504279332479712</v>
+        <v>-0.131612663300696</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
         <v>21</v>
       </c>
       <c r="C46">
-        <v>0.356718749874893</v>
+        <v>0.3491435192167209</v>
       </c>
       <c r="D46">
-        <v>0.001347090050993563</v>
+        <v>0.001730350710648835</v>
       </c>
       <c r="E46">
-        <v>0.004071205487447212</v>
+        <v>0.005229504369960923</v>
       </c>
       <c r="F46">
-        <v>0.1178549156284804</v>
+        <v>0.1192776971503078</v>
       </c>
       <c r="G46">
-        <v>0.5563832237547441</v>
+        <v>0.5426333896641405</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1494,45 +1494,45 @@
         <v>18</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C47">
-        <v>0.3531777405522082</v>
+        <v>0.3434413687578244</v>
       </c>
       <c r="D47">
-        <v>0.001515498712453361</v>
+        <v>0.002080893045824373</v>
       </c>
       <c r="E47">
-        <v>0.004480604888992545</v>
+        <v>0.006152205526785102</v>
       </c>
       <c r="F47">
-        <v>0.1204803901929458</v>
+        <v>0.1254301636162643</v>
       </c>
       <c r="G47">
-        <v>0.549555616388635</v>
+        <v>0.5355905382537294</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
         <v>20</v>
       </c>
       <c r="C48">
-        <v>-0.3507252241429456</v>
+        <v>-0.3407965705799805</v>
       </c>
       <c r="D48">
-        <v>0.001643040891718564</v>
+        <v>0.002264175749507698</v>
       </c>
       <c r="E48">
-        <v>0.004754331090930313</v>
+        <v>0.006551657487937169</v>
       </c>
       <c r="F48">
-        <v>-0.5392041442621492</v>
+        <v>-0.5435378532967599</v>
       </c>
       <c r="G48">
-        <v>-0.1424339684144761</v>
+        <v>-0.08456827636489016</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1540,206 +1540,206 @@
         <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C49">
-        <v>0.3483082839246133</v>
+        <v>-0.3401029350396438</v>
       </c>
       <c r="D49">
-        <v>0.001778122810723413</v>
+        <v>0.002314583528513864</v>
       </c>
       <c r="E49">
-        <v>0.005038014630383003</v>
+        <v>0.006557986664122615</v>
       </c>
       <c r="F49">
-        <v>0.1295852743584832</v>
+        <v>-0.5411818978237725</v>
       </c>
       <c r="G49">
-        <v>0.5547354860586671</v>
+        <v>-0.1161376342994641</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" t="s">
         <v>22</v>
       </c>
-      <c r="B50" t="s">
-        <v>20</v>
-      </c>
       <c r="C50">
-        <v>-0.341201242005954</v>
+        <v>0.3318558612623789</v>
       </c>
       <c r="D50">
-        <v>0.002235224879154514</v>
+        <v>0.002995923922568968</v>
       </c>
       <c r="E50">
-        <v>0.006203889460510489</v>
+        <v>0.008148913069387592</v>
       </c>
       <c r="F50">
-        <v>-0.5362625279127112</v>
+        <v>0.107084869325419</v>
       </c>
       <c r="G50">
-        <v>-0.1007417095670578</v>
+        <v>0.5414496027668703</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C51">
-        <v>-0.3258387182437815</v>
+        <v>-0.3323132563638892</v>
       </c>
       <c r="D51">
-        <v>0.003600841713820929</v>
+        <v>0.002953891580925661</v>
       </c>
       <c r="E51">
-        <v>0.009602244570189145</v>
+        <v>0.008148913069387592</v>
       </c>
       <c r="F51">
-        <v>-0.5293207437209834</v>
+        <v>-0.5340735383809282</v>
       </c>
       <c r="G51">
-        <v>-0.09593669115829336</v>
+        <v>-0.08788852007146666</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C52">
-        <v>0.3260640014781334</v>
+        <v>0.3244729953590713</v>
       </c>
       <c r="D52">
-        <v>0.003576365487923153</v>
+        <v>0.003752444881019965</v>
       </c>
       <c r="E52">
-        <v>0.009602244570189145</v>
+        <v>0.01000651968271991</v>
       </c>
       <c r="F52">
-        <v>0.07725742898061569</v>
+        <v>0.07868137584540402</v>
       </c>
       <c r="G52">
-        <v>0.5439205074477053</v>
+        <v>0.5256694846613342</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C53">
-        <v>-0.3251305656368947</v>
+        <v>0.317730299299492</v>
       </c>
       <c r="D53">
-        <v>0.003678755245503657</v>
+        <v>0.00458739821423427</v>
       </c>
       <c r="E53">
-        <v>0.009621359872855718</v>
+        <v>0.01177143692709171</v>
       </c>
       <c r="F53">
-        <v>-0.524669467850734</v>
+        <v>0.06486359257251584</v>
       </c>
       <c r="G53">
-        <v>-0.07955136204409791</v>
+        <v>0.5311193071300978</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C54">
-        <v>0.3206135832095531</v>
+        <v>0.3183272423778752</v>
       </c>
       <c r="D54">
-        <v>0.004212052014775776</v>
+        <v>0.004507337418634326</v>
       </c>
       <c r="E54">
-        <v>0.01080828441527369</v>
+        <v>0.01177143692709171</v>
       </c>
       <c r="F54">
-        <v>0.0620349811612578</v>
+        <v>0.07186009333474561</v>
       </c>
       <c r="G54">
-        <v>0.5391229976278666</v>
+        <v>0.5355350379392914</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C55">
-        <v>0.318807774503977</v>
+        <v>0.3158467185020382</v>
       </c>
       <c r="D55">
-        <v>0.00444379322832955</v>
+        <v>0.004848358080970575</v>
       </c>
       <c r="E55">
-        <v>0.01119177553801516</v>
+        <v>0.0119886672547636</v>
       </c>
       <c r="F55">
-        <v>0.08256615274248488</v>
+        <v>0.05539338175299277</v>
       </c>
       <c r="G55">
-        <v>0.5350630704442835</v>
+        <v>0.5377665681212586</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3165296576707381</v>
+        <v>0.3158487082537715</v>
       </c>
       <c r="D56">
-        <v>0.004752257744581647</v>
+        <v>0.004848075606977623</v>
       </c>
       <c r="E56">
-        <v>0.01175103733205644</v>
+        <v>0.0119886672547636</v>
       </c>
       <c r="F56">
-        <v>0.05682896516435602</v>
+        <v>0.08707489511927878</v>
       </c>
       <c r="G56">
-        <v>0.5344659427696145</v>
+        <v>0.5085999841625014</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C57">
-        <v>0.3062973064122349</v>
+        <v>0.3040220547446403</v>
       </c>
       <c r="D57">
-        <v>0.006384444468212902</v>
+        <v>0.006808377283659248</v>
       </c>
       <c r="E57">
-        <v>0.01550507942280276</v>
+        <v>0.0165346305460296</v>
       </c>
       <c r="F57">
-        <v>0.07002415393658448</v>
+        <v>0.06287125337921425</v>
       </c>
       <c r="G57">
-        <v>0.54651767774544</v>
+        <v>0.5118281170842244</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1750,88 +1750,88 @@
         <v>19</v>
       </c>
       <c r="C58">
-        <v>0.3053275838085964</v>
+        <v>0.3021661882421375</v>
       </c>
       <c r="D58">
-        <v>0.006562193376679045</v>
+        <v>0.007172328974041265</v>
       </c>
       <c r="E58">
-        <v>0.01565716314435702</v>
+        <v>0.0171129252713967</v>
       </c>
       <c r="F58">
-        <v>0.09251923728297334</v>
+        <v>0.1052040652281995</v>
       </c>
       <c r="G58">
-        <v>0.4914543527794276</v>
+        <v>0.4763967969794658</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C59">
-        <v>0.3019891500904159</v>
+        <v>0.2975080154148566</v>
       </c>
       <c r="D59">
-        <v>0.00720792593318473</v>
+        <v>0.008162216482957573</v>
       </c>
       <c r="E59">
-        <v>0.01690134356746764</v>
+        <v>0.01913899037383155</v>
       </c>
       <c r="F59">
-        <v>0.08389217904433156</v>
+        <v>0.053050960997991</v>
       </c>
       <c r="G59">
-        <v>0.5030325155124136</v>
+        <v>0.548480878332118</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C60">
-        <v>0.2976137786264368</v>
+        <v>0.2950754372117669</v>
       </c>
       <c r="D60">
-        <v>0.008138475379727617</v>
+        <v>0.00872529199769659</v>
       </c>
       <c r="E60">
-        <v>0.01875987545157552</v>
+        <v>0.02011253748621587</v>
       </c>
       <c r="F60">
-        <v>0.06994310200103315</v>
+        <v>0.06918271058902677</v>
       </c>
       <c r="G60">
-        <v>0.4920218310223169</v>
+        <v>0.5130724773018351</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C61">
-        <v>0.2952271957137081</v>
+        <v>-0.2879160793169542</v>
       </c>
       <c r="D61">
-        <v>0.00868919438462535</v>
+        <v>0.01058450829104361</v>
       </c>
       <c r="E61">
-        <v>0.01969550727181746</v>
+        <v>0.02399155212636553</v>
       </c>
       <c r="F61">
-        <v>0.06348496218924102</v>
+        <v>-0.5060810661324058</v>
       </c>
       <c r="G61">
-        <v>0.4970026150784886</v>
+        <v>-0.02821046516996546</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1842,456 +1842,456 @@
         <v>15</v>
       </c>
       <c r="C62">
-        <v>-0.2896217706344288</v>
+        <v>-0.2836783469694861</v>
       </c>
       <c r="D62">
-        <v>0.01011275367387617</v>
+        <v>0.01184045750075065</v>
       </c>
       <c r="E62">
-        <v>0.02254646720733047</v>
+        <v>0.02602442610266922</v>
       </c>
       <c r="F62">
-        <v>-0.5122138580494736</v>
+        <v>-0.5067120324208002</v>
       </c>
       <c r="G62">
-        <v>-0.04060304446542919</v>
+        <v>-0.0432557827850571</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C63">
-        <v>0.2860304252709315</v>
+        <v>0.2836024734758912</v>
       </c>
       <c r="D63">
-        <v>0.01112825461316306</v>
+        <v>0.01186407660562861</v>
       </c>
       <c r="E63">
-        <v>0.02441036495790607</v>
+        <v>0.02602442610266922</v>
       </c>
       <c r="F63">
-        <v>0.06078601211860639</v>
+        <v>0.04893305553381305</v>
       </c>
       <c r="G63">
-        <v>0.4731847632585871</v>
+        <v>0.4866835446535197</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C64">
-        <v>-0.2758341607291749</v>
+        <v>0.2823379152493076</v>
       </c>
       <c r="D64">
-        <v>0.01450960792532629</v>
+        <v>0.0122637995704948</v>
       </c>
       <c r="E64">
-        <v>0.03057687027766376</v>
+        <v>0.02647423399344909</v>
       </c>
       <c r="F64">
-        <v>-0.4760528145492136</v>
+        <v>0.0656666539314044</v>
       </c>
       <c r="G64">
-        <v>-0.06859154222750299</v>
+        <v>0.4880116944910271</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C65">
-        <v>0.2757116301420098</v>
+        <v>0.2775073028237585</v>
       </c>
       <c r="D65">
-        <v>0.01455512185198705</v>
+        <v>0.01390031786904699</v>
       </c>
       <c r="E65">
-        <v>0.03057687027766376</v>
+        <v>0.0290837420029291</v>
       </c>
       <c r="F65">
-        <v>0.03605427656343282</v>
+        <v>0.04206336936265086</v>
       </c>
       <c r="G65">
-        <v>0.474202222427033</v>
+        <v>0.4724075769947998</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>-0.2755537576142108</v>
+        <v>0.2775301157057752</v>
       </c>
       <c r="D66">
-        <v>0.01461394535329518</v>
+        <v>0.01389216572577034</v>
       </c>
       <c r="E66">
-        <v>0.03057687027766376</v>
+        <v>0.0290837420029291</v>
       </c>
       <c r="F66">
-        <v>-0.4944883680770814</v>
+        <v>0.04008434612808572</v>
       </c>
       <c r="G66">
-        <v>-0.02713197534577454</v>
+        <v>0.4836056356598359</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B67" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>0.2737153587945226</v>
+        <v>-0.2767172321059501</v>
       </c>
       <c r="D67">
-        <v>0.01531420037384691</v>
+        <v>0.01418521379746462</v>
       </c>
       <c r="E67">
-        <v>0.03138744134233346</v>
+        <v>0.02923013752204831</v>
       </c>
       <c r="F67">
-        <v>0.03800777300291842</v>
+        <v>-0.4880767948774941</v>
       </c>
       <c r="G67">
-        <v>0.5014834421235859</v>
+        <v>-0.01321619778370622</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
         <v>19</v>
       </c>
-      <c r="B68" t="s">
-        <v>8</v>
-      </c>
       <c r="C68">
-        <v>0.2733342606760328</v>
+        <v>0.2736124634858811</v>
       </c>
       <c r="D68">
-        <v>0.01546293066129663</v>
+        <v>0.01535423494750343</v>
       </c>
       <c r="E68">
-        <v>0.03138744134233346</v>
+        <v>0.03116680526657413</v>
       </c>
       <c r="F68">
-        <v>0.03682140626793867</v>
+        <v>0.03921995940503631</v>
       </c>
       <c r="G68">
-        <v>0.4760289711900768</v>
+        <v>0.4719526557179106</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C69">
-        <v>0.2721202847785126</v>
+        <v>-0.2682777240390759</v>
       </c>
       <c r="D69">
-        <v>0.01594504128660476</v>
+        <v>0.01755738922619413</v>
       </c>
       <c r="E69">
-        <v>0.03189008257320953</v>
+        <v>0.03511477845238825</v>
       </c>
       <c r="F69">
-        <v>0.04208761451637395</v>
+        <v>-0.4751706808719712</v>
       </c>
       <c r="G69">
-        <v>0.4855040329499205</v>
+        <v>-0.01863193875828251</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C70">
-        <v>0.2701318419446507</v>
+        <v>-0.2648832264234586</v>
       </c>
       <c r="D70">
-        <v>0.0167627092541639</v>
+        <v>0.01909633445587158</v>
       </c>
       <c r="E70">
-        <v>0.03303954287777232</v>
+        <v>0.03710144979997906</v>
       </c>
       <c r="F70">
-        <v>0.03600461267128688</v>
+        <v>-0.4918707276119498</v>
       </c>
       <c r="G70">
-        <v>0.4669066762674781</v>
+        <v>-0.01059091239052343</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B71" t="s">
         <v>10</v>
       </c>
       <c r="C71">
-        <v>-0.2691160432069948</v>
+        <v>-0.2652115357973711</v>
       </c>
       <c r="D71">
-        <v>0.01719416202825624</v>
+        <v>0.01894260778695053</v>
       </c>
       <c r="E71">
-        <v>0.03340580051204069</v>
+        <v>0.03710144979997906</v>
       </c>
       <c r="F71">
-        <v>-0.4939011805114018</v>
+        <v>-0.4809242646859089</v>
       </c>
       <c r="G71">
-        <v>-0.009585119188993413</v>
+        <v>-0.04725395992781879</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C72">
-        <v>-0.2653986487352255</v>
+        <v>0.2634454153441495</v>
       </c>
       <c r="D72">
-        <v>0.0188554699234945</v>
+        <v>0.01978222520443689</v>
       </c>
       <c r="E72">
-        <v>0.03611751985345425</v>
+        <v>0.03789271306765375</v>
       </c>
       <c r="F72">
-        <v>-0.4832041131217334</v>
+        <v>0.02258385999945878</v>
       </c>
       <c r="G72">
-        <v>-0.02961305870745819</v>
+        <v>0.4721607282461032</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C73">
-        <v>-0.2623162296636679</v>
+        <v>-0.2621611544973422</v>
       </c>
       <c r="D73">
-        <v>0.02033556835568369</v>
+        <v>0.02041258474484281</v>
       </c>
       <c r="E73">
-        <v>0.03817343319503822</v>
+        <v>0.03855710451803642</v>
       </c>
       <c r="F73">
-        <v>-0.4560916389135982</v>
+        <v>-0.4863288190522488</v>
       </c>
       <c r="G73">
-        <v>-0.04884776277395177</v>
+        <v>-0.01996643244949976</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C74">
-        <v>-0.2620054755769792</v>
+        <v>0.2581807843305264</v>
       </c>
       <c r="D74">
-        <v>0.02049015164145434</v>
+        <v>0.0224764864303201</v>
       </c>
       <c r="E74">
-        <v>0.03817343319503822</v>
+        <v>0.04130813722329101</v>
       </c>
       <c r="F74">
-        <v>-0.4798770658162372</v>
+        <v>0.02715604011544271</v>
       </c>
       <c r="G74">
-        <v>-0.0294775230549154</v>
+        <v>0.455460547872061</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C75">
-        <v>0.2593189802937763</v>
+        <v>0.2587412587412587</v>
       </c>
       <c r="D75">
-        <v>0.021868912456206</v>
+        <v>0.02217552917306276</v>
       </c>
       <c r="E75">
-        <v>0.0401915147843786</v>
+        <v>0.04130813722329101</v>
       </c>
       <c r="F75">
-        <v>0.03168592134234885</v>
+        <v>0.01904241260683581</v>
       </c>
       <c r="G75">
-        <v>0.4742104463928029</v>
+        <v>0.4692146361167619</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C76">
-        <v>-0.2577611916396096</v>
+        <v>0.2571368956215211</v>
       </c>
       <c r="D76">
-        <v>0.02270406594417261</v>
+        <v>0.02304630333673224</v>
       </c>
       <c r="E76">
-        <v>0.04117003957876633</v>
+        <v>0.04179063005060778</v>
       </c>
       <c r="F76">
-        <v>-0.4854591343869314</v>
+        <v>0.02135406049219331</v>
       </c>
       <c r="G76">
-        <v>0.004989902000489538</v>
+        <v>0.4931992759772857</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C77">
-        <v>0.2546693812516597</v>
+        <v>-0.2558032194295154</v>
       </c>
       <c r="D77">
-        <v>0.02444228966903218</v>
+        <v>0.02379215334232557</v>
       </c>
       <c r="E77">
-        <v>0.04373883414458389</v>
+        <v>0.04202250460462698</v>
       </c>
       <c r="F77">
-        <v>0.04037917862651796</v>
+        <v>-0.4496100997997832</v>
       </c>
       <c r="G77">
-        <v>0.4443523218602778</v>
+        <v>-0.03639353945292678</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B78" t="s">
         <v>10</v>
       </c>
       <c r="C78">
-        <v>-0.2504457567748706</v>
+        <v>0.2560098129718382</v>
       </c>
       <c r="D78">
-        <v>0.02699848867038768</v>
+        <v>0.02367529130679335</v>
       </c>
       <c r="E78">
-        <v>0.0476856423269185</v>
+        <v>0.04202250460462698</v>
       </c>
       <c r="F78">
-        <v>-0.4619673163327423</v>
+        <v>0.04555533250352671</v>
       </c>
       <c r="G78">
-        <v>-0.01979890641564315</v>
+        <v>0.44675560207105</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B79" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>0.2428584074153694</v>
+        <v>0.252873708569911</v>
       </c>
       <c r="D79">
-        <v>0.03215933334745421</v>
+        <v>0.02550276768013224</v>
       </c>
       <c r="E79">
-        <v>0.05607268378530478</v>
+        <v>0.04446636416023057</v>
       </c>
       <c r="F79">
-        <v>0.01017420493107042</v>
+        <v>0.02546148366265676</v>
       </c>
       <c r="G79">
-        <v>0.4466231001516138</v>
+        <v>0.4570830017822731</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C80">
-        <v>0.2395199736971888</v>
+        <v>-0.2417708873405076</v>
       </c>
       <c r="D80">
-        <v>0.03467968382338219</v>
+        <v>0.03296289621437429</v>
       </c>
       <c r="E80">
-        <v>0.05970173417696175</v>
+        <v>0.05674625171082157</v>
       </c>
       <c r="F80">
-        <v>0.0174741557110501</v>
+        <v>-0.4399912951673774</v>
       </c>
       <c r="G80">
-        <v>0.4501188944854642</v>
+        <v>-0.03234384252499211</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C81">
-        <v>-0.2312497628953324</v>
+        <v>0.2328431062608277</v>
       </c>
       <c r="D81">
-        <v>0.0416430366040943</v>
+        <v>0.04021797320869028</v>
       </c>
       <c r="E81">
-        <v>0.0707931622269603</v>
+        <v>0.06837055445477347</v>
       </c>
       <c r="F81">
-        <v>-0.4271000306464488</v>
+        <v>-0.004844445929343873</v>
       </c>
       <c r="G81">
-        <v>-0.01697186971076453</v>
+        <v>0.4541183641421654</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2299,45 +2299,45 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C82">
-        <v>0.2284944706887609</v>
+        <v>0.230922437835379</v>
       </c>
       <c r="D82">
-        <v>0.04420611598810811</v>
+        <v>0.04194091923757882</v>
       </c>
       <c r="E82">
-        <v>0.07422261449855189</v>
+        <v>0.07041932118902124</v>
       </c>
       <c r="F82">
-        <v>-0.01853385378941209</v>
+        <v>-0.02241161294237326</v>
       </c>
       <c r="G82">
-        <v>0.4509844122764456</v>
+        <v>0.4550461914348861</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C83">
-        <v>0.2274560882155818</v>
+        <v>-0.2256098332047698</v>
       </c>
       <c r="D83">
-        <v>0.04520531243085261</v>
+        <v>0.04702795790410471</v>
       </c>
       <c r="E83">
-        <v>0.07497466451946286</v>
+        <v>0.07799758871900293</v>
       </c>
       <c r="F83">
-        <v>-0.01105903745592425</v>
+        <v>-0.4456718054018916</v>
       </c>
       <c r="G83">
-        <v>0.4548850316957926</v>
+        <v>-0.001916627438326386</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2348,19 +2348,19 @@
         <v>22</v>
       </c>
       <c r="C84">
-        <v>-0.2255537360519698</v>
+        <v>-0.222581930267477</v>
       </c>
       <c r="D84">
-        <v>0.04708427235409161</v>
+        <v>0.05014803840340822</v>
       </c>
       <c r="E84">
-        <v>0.07715013301393324</v>
+        <v>0.08217027979353636</v>
       </c>
       <c r="F84">
-        <v>-0.437509314384672</v>
+        <v>-0.4321217772849912</v>
       </c>
       <c r="G84">
-        <v>0.01099244484647048</v>
+        <v>0.01435095974613457</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2371,88 +2371,88 @@
         <v>23</v>
       </c>
       <c r="C85">
-        <v>-0.2192870420718522</v>
+        <v>-0.2214114998925125</v>
       </c>
       <c r="D85">
-        <v>0.05373440586738597</v>
+        <v>0.05139879704732437</v>
       </c>
       <c r="E85">
-        <v>0.08699856188052968</v>
+        <v>0.08321709998138231</v>
       </c>
       <c r="F85">
-        <v>-0.4497677987712963</v>
+        <v>-0.4377761838154072</v>
       </c>
       <c r="G85">
-        <v>0.02995153237486736</v>
+        <v>0.0236149230797665</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C86">
-        <v>0.2169797602141566</v>
+        <v>0.2146474705557047</v>
       </c>
       <c r="D86">
-        <v>0.05636865194037977</v>
+        <v>0.0591375892452406</v>
       </c>
       <c r="E86">
-        <v>0.09003954173576487</v>
+        <v>0.09462014279238497</v>
       </c>
       <c r="F86">
-        <v>-0.01187221246451871</v>
+        <v>-0.0139213119781183</v>
       </c>
       <c r="G86">
-        <v>0.4369011201470607</v>
+        <v>0.425286545244003</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
         <v>19</v>
       </c>
       <c r="C87">
-        <v>0.2164937372401122</v>
+        <v>0.2119526043576676</v>
       </c>
       <c r="D87">
-        <v>0.0569367690387925</v>
+        <v>0.06247371090604058</v>
       </c>
       <c r="E87">
-        <v>0.09003954173576487</v>
+        <v>0.09879563585141302</v>
       </c>
       <c r="F87">
-        <v>0.006156985290643509</v>
+        <v>-0.02496526444293899</v>
       </c>
       <c r="G87">
-        <v>0.4208824209461349</v>
+        <v>0.4301071553363313</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C88">
-        <v>-0.2148863794433414</v>
+        <v>-0.2092464497527788</v>
       </c>
       <c r="D88">
-        <v>0.05884896162053195</v>
+        <v>0.06597571436032912</v>
       </c>
       <c r="E88">
-        <v>0.09199377908496949</v>
+        <v>0.1031344500345375</v>
       </c>
       <c r="F88">
-        <v>-0.4240072281504082</v>
+        <v>-0.441300812575001</v>
       </c>
       <c r="G88">
-        <v>0.0185354168904864</v>
+        <v>0.07499241501538635</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2460,137 +2460,137 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C89">
-        <v>-0.2107892107892108</v>
+        <v>-0.208386550158702</v>
       </c>
       <c r="D89">
-        <v>0.06396032069137984</v>
+        <v>0.06712112085085258</v>
       </c>
       <c r="E89">
-        <v>0.09884776834122339</v>
+        <v>0.103732641314954</v>
       </c>
       <c r="F89">
-        <v>-0.4427581994189347</v>
+        <v>-0.4252754167046106</v>
       </c>
       <c r="G89">
-        <v>0.05010305830028633</v>
+        <v>0.02256108588931855</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C90">
-        <v>0.2051745722631798</v>
+        <v>0.206420365192661</v>
       </c>
       <c r="D90">
-        <v>0.07154215678333288</v>
+        <v>0.06980044060485116</v>
       </c>
       <c r="E90">
-        <v>0.1093228463205985</v>
+        <v>0.1066613474411209</v>
       </c>
       <c r="F90">
-        <v>-0.01979135245858682</v>
+        <v>-0.03268074102941101</v>
       </c>
       <c r="G90">
-        <v>0.4078050146483063</v>
+        <v>0.4301045053687888</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C91">
-        <v>-0.2040364698592546</v>
+        <v>-0.2010711147805741</v>
       </c>
       <c r="D91">
-        <v>0.07316366112893229</v>
+        <v>0.07752720342368585</v>
       </c>
       <c r="E91">
-        <v>0.1105584212614977</v>
+        <v>0.1171522185069031</v>
       </c>
       <c r="F91">
-        <v>-0.4349830068602832</v>
+        <v>-0.4294421974876092</v>
       </c>
       <c r="G91">
-        <v>0.04368948356313407</v>
+        <v>0.06665523604334804</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C92">
-        <v>-0.2030438879821948</v>
+        <v>-0.199880328472717</v>
       </c>
       <c r="D92">
-        <v>0.07460177329007286</v>
+        <v>0.07933688639955189</v>
       </c>
       <c r="E92">
-        <v>0.1114927600818671</v>
+        <v>0.1185694126410885</v>
       </c>
       <c r="F92">
-        <v>-0.4323824190993368</v>
+        <v>-0.4189409436409086</v>
       </c>
       <c r="G92">
-        <v>0.06587484443179935</v>
+        <v>0.04587928995829086</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C93">
-        <v>0.201440418075505</v>
+        <v>-0.1966767409805384</v>
       </c>
       <c r="D93">
-        <v>0.07697270405403153</v>
+        <v>0.08437294188712954</v>
       </c>
       <c r="E93">
-        <v>0.1137857364276988</v>
+        <v>0.1247252184418437</v>
       </c>
       <c r="F93">
-        <v>-0.01535464361977266</v>
+        <v>-0.4059762155485224</v>
       </c>
       <c r="G93">
-        <v>0.4104322312271829</v>
+        <v>0.02711310967943132</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C94">
-        <v>-0.1898196182140907</v>
+        <v>0.1955272292760873</v>
       </c>
       <c r="D94">
-        <v>0.09600334184136976</v>
+        <v>0.08624058696872218</v>
       </c>
       <c r="E94">
-        <v>0.1403919837680246</v>
+        <v>0.1261152669650131</v>
       </c>
       <c r="F94">
-        <v>-0.4211677395652131</v>
+        <v>-0.04652081081061619</v>
       </c>
       <c r="G94">
-        <v>0.05452908207970179</v>
+        <v>0.4232030320670192</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2598,114 +2598,114 @@
         <v>15</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C95">
-        <v>-0.1862820723580217</v>
+        <v>-0.1849922229669065</v>
       </c>
       <c r="D95">
-        <v>0.1024764332078764</v>
+        <v>0.1049195361946959</v>
       </c>
       <c r="E95">
-        <v>0.1482637757050126</v>
+        <v>0.1517984778987089</v>
       </c>
       <c r="F95">
-        <v>-0.4331628181570191</v>
+        <v>-0.4219885139894232</v>
       </c>
       <c r="G95">
-        <v>0.0885650012798334</v>
+        <v>0.08350522777082214</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C96">
-        <v>0.1842599442363128</v>
+        <v>0.1789476346438371</v>
       </c>
       <c r="D96">
-        <v>0.1063265739746315</v>
+        <v>0.1169771105170091</v>
       </c>
       <c r="E96">
-        <v>0.1522148848478935</v>
+        <v>0.1674619687401394</v>
       </c>
       <c r="F96">
-        <v>-0.06571734858458052</v>
+        <v>-0.06007160618343799</v>
       </c>
       <c r="G96">
-        <v>0.4096576056759329</v>
+        <v>0.3914262291915588</v>
       </c>
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C97">
-        <v>0.1820078655521693</v>
+        <v>0.1755818259847406</v>
       </c>
       <c r="D97">
-        <v>0.1107458273494377</v>
+        <v>0.1241384760192209</v>
       </c>
       <c r="E97">
-        <v>0.15688992207837</v>
+        <v>0.1748589332748514</v>
       </c>
       <c r="F97">
-        <v>-0.05160009653702735</v>
+        <v>-0.0493290113395215</v>
       </c>
       <c r="G97">
-        <v>0.3897837471084674</v>
+        <v>0.3918552413723051</v>
       </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C98">
-        <v>0.1788864655574477</v>
+        <v>0.1753171364151548</v>
       </c>
       <c r="D98">
-        <v>0.1171043584564306</v>
+        <v>0.1247155627033867</v>
       </c>
       <c r="E98">
-        <v>0.1625121709191283</v>
+        <v>0.1748589332748514</v>
       </c>
       <c r="F98">
-        <v>-0.08879700727219397</v>
+        <v>-0.03470863060130761</v>
       </c>
       <c r="G98">
-        <v>0.4333641653927918</v>
+        <v>0.3756609141553326</v>
       </c>
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C99">
-        <v>0.1788995036685524</v>
+        <v>0.1737376547503129</v>
       </c>
       <c r="D99">
-        <v>0.1170772267957179</v>
+        <v>0.1282019241797591</v>
       </c>
       <c r="E99">
-        <v>0.1625121709191283</v>
+        <v>0.1779128743719105</v>
       </c>
       <c r="F99">
-        <v>-0.0374594230455871</v>
+        <v>-0.05837962427544803</v>
       </c>
       <c r="G99">
-        <v>0.391281061413193</v>
+        <v>0.3781638100412221</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2713,160 +2713,160 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C100">
-        <v>0.1721443113848177</v>
+        <v>0.1667962951033707</v>
       </c>
       <c r="D100">
-        <v>0.131793627349937</v>
+        <v>0.1444089103312658</v>
       </c>
       <c r="E100">
-        <v>0.1810498315110246</v>
+        <v>0.198379917222749</v>
       </c>
       <c r="F100">
-        <v>-0.07583699866475613</v>
+        <v>-0.0929712809696958</v>
       </c>
       <c r="G100">
-        <v>0.404199226521729</v>
+        <v>0.411843619780021</v>
       </c>
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C101">
-        <v>0.1696910684252456</v>
+        <v>-0.1649245950749152</v>
       </c>
       <c r="D101">
-        <v>0.1374724347406798</v>
+        <v>0.1490318161994552</v>
       </c>
       <c r="E101">
-        <v>0.1869625112473245</v>
+        <v>0.2026832700312591</v>
       </c>
       <c r="F101">
-        <v>-0.05782202524697419</v>
+        <v>-0.4180348479377226</v>
       </c>
       <c r="G101">
-        <v>0.3945445722099508</v>
+        <v>0.1114805573536445</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C102">
-        <v>0.1676920843528586</v>
+        <v>0.157905385753487</v>
       </c>
       <c r="D102">
-        <v>0.1422348937862846</v>
+        <v>0.1673569232790886</v>
       </c>
       <c r="E102">
-        <v>0.1915242134151951</v>
+        <v>0.2253518966926341</v>
       </c>
       <c r="F102">
-        <v>-0.1204815976778257</v>
+        <v>-0.0768187659053572</v>
       </c>
       <c r="G102">
-        <v>0.4100296928703454</v>
+        <v>0.3817427319709198</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C103">
-        <v>-0.1652398234676715</v>
+        <v>0.1543247741597235</v>
       </c>
       <c r="D103">
-        <v>0.1482455776306059</v>
+        <v>0.1773203418906445</v>
       </c>
       <c r="E103">
-        <v>0.1957417335705088</v>
+        <v>0.2364271225208593</v>
       </c>
       <c r="F103">
-        <v>-0.3942469106065725</v>
+        <v>-0.1213268090887349</v>
       </c>
       <c r="G103">
-        <v>0.07894126657854768</v>
+        <v>0.3974807385565461</v>
       </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C104">
-        <v>-0.165746625492818</v>
+        <v>0.1475360082955019</v>
       </c>
       <c r="D104">
-        <v>0.1469880343137341</v>
+        <v>0.1973867235447058</v>
       </c>
       <c r="E104">
-        <v>0.1957417335705088</v>
+        <v>0.2606271301172814</v>
       </c>
       <c r="F104">
-        <v>-0.4058529687368586</v>
+        <v>-0.1143647511101459</v>
       </c>
       <c r="G104">
-        <v>0.09137109609472235</v>
+        <v>0.3898757389009563</v>
       </c>
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B105" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C105">
-        <v>0.1588664500056905</v>
+        <v>0.1456454356645866</v>
       </c>
       <c r="D105">
-        <v>0.1647542267574055</v>
+        <v>0.2032541612767126</v>
       </c>
       <c r="E105">
-        <v>0.2154478349904533</v>
+        <v>0.2657939032080088</v>
       </c>
       <c r="F105">
-        <v>-0.07908196273028528</v>
+        <v>-0.07444412102725449</v>
       </c>
       <c r="G105">
-        <v>0.3897877621195068</v>
+        <v>0.375475414370603</v>
       </c>
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B106" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C106">
-        <v>0.1568609674126053</v>
+        <v>-0.1414155464788376</v>
       </c>
       <c r="D106">
-        <v>0.1702195439430042</v>
+        <v>0.2168300141542445</v>
       </c>
       <c r="E106">
-        <v>0.220474837869034</v>
+        <v>0.2808464945235929</v>
       </c>
       <c r="F106">
-        <v>-0.06309915042620132</v>
+        <v>-0.3741547555655305</v>
       </c>
       <c r="G106">
-        <v>0.3692671726032013</v>
+        <v>0.1047545545577793</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -2877,203 +2877,203 @@
         <v>19</v>
       </c>
       <c r="C107">
-        <v>0.1453149798706652</v>
+        <v>0.134970566544218</v>
       </c>
       <c r="D107">
-        <v>0.2042923856939212</v>
+        <v>0.2387238425502427</v>
       </c>
       <c r="E107">
-        <v>0.2621109854186159</v>
+        <v>0.3062871942154057</v>
       </c>
       <c r="F107">
-        <v>-0.07133765176598975</v>
+        <v>-0.08112272759151846</v>
       </c>
       <c r="G107">
-        <v>0.3461733512291567</v>
+        <v>0.3488916297604335</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B108" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C108">
-        <v>0.1335752854740196</v>
+        <v>-0.1218907674603877</v>
       </c>
       <c r="D108">
-        <v>0.2436581678655761</v>
+        <v>0.2877366961392889</v>
       </c>
       <c r="E108">
-        <v>0.3096963628945639</v>
+        <v>0.3657214081770401</v>
       </c>
       <c r="F108">
-        <v>-0.1249057343860715</v>
+        <v>-0.3412971363415401</v>
       </c>
       <c r="G108">
-        <v>0.3751521516852575</v>
+        <v>0.1308975258996668</v>
       </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C109">
-        <v>0.1258867714563917</v>
+        <v>0.1125583277482011</v>
       </c>
       <c r="D109">
-        <v>0.2721051373349933</v>
+        <v>0.326513356093723</v>
       </c>
       <c r="E109">
-        <v>0.3426509136811026</v>
+        <v>0.4111649669328364</v>
       </c>
       <c r="F109">
-        <v>-0.1276467096991621</v>
+        <v>-0.1398592120808738</v>
       </c>
       <c r="G109">
-        <v>0.3486511342950769</v>
+        <v>0.3454399860139024</v>
       </c>
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B110" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C110">
-        <v>0.1165290405796735</v>
+        <v>-0.1090757336005585</v>
       </c>
       <c r="D110">
-        <v>0.3096259648395562</v>
+        <v>0.3417983428583803</v>
       </c>
       <c r="E110">
-        <v>0.3863223047539417</v>
+        <v>0.4264639874196305</v>
       </c>
       <c r="F110">
-        <v>-0.1182410664824514</v>
+        <v>-0.3219359086205341</v>
       </c>
       <c r="G110">
-        <v>0.3362901198868941</v>
+        <v>0.1115416676292746</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C111">
-        <v>-0.1092704763590839</v>
+        <v>-0.1056445341432023</v>
       </c>
       <c r="D111">
-        <v>0.3409319643193083</v>
+        <v>0.3572891036438902</v>
       </c>
       <c r="E111">
-        <v>0.4215158831584175</v>
+        <v>0.4417392554142642</v>
       </c>
       <c r="F111">
-        <v>-0.3329464267246267</v>
+        <v>-0.3126369704906997</v>
       </c>
       <c r="G111">
-        <v>0.1413365330910296</v>
+        <v>0.1094894066448799</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C112">
-        <v>-0.1043134081108764</v>
+        <v>0.1034029261877363</v>
       </c>
       <c r="D112">
-        <v>0.3634135289118285</v>
+        <v>0.3676394400433616</v>
       </c>
       <c r="E112">
-        <v>0.4429535851747813</v>
+        <v>0.4504411157288034</v>
       </c>
       <c r="F112">
-        <v>-0.3098565284717891</v>
+        <v>-0.1237665496957301</v>
       </c>
       <c r="G112">
-        <v>0.112086123620021</v>
+        <v>0.3031747995349983</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113" t="s">
         <v>21</v>
       </c>
-      <c r="B113" t="s">
-        <v>19</v>
-      </c>
       <c r="C113">
-        <v>-0.1040171488538659</v>
+        <v>-0.09453230245381733</v>
       </c>
       <c r="D113">
-        <v>0.3647853054380552</v>
+        <v>0.4103640150876002</v>
       </c>
       <c r="E113">
-        <v>0.4429535851747813</v>
+        <v>0.4938894340877313</v>
       </c>
       <c r="F113">
-        <v>-0.3118183618956766</v>
+        <v>-0.3132755081546089</v>
       </c>
       <c r="G113">
-        <v>0.1174909165854151</v>
+        <v>0.1343019962414222</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C114">
-        <v>-0.1019013234529475</v>
+        <v>-0.09466682312280356</v>
       </c>
       <c r="D114">
-        <v>0.3746741932213787</v>
+        <v>0.4096952736931921</v>
       </c>
       <c r="E114">
-        <v>0.4509353121956417</v>
+        <v>0.4938894340877313</v>
       </c>
       <c r="F114">
-        <v>-0.3054185930794282</v>
+        <v>-0.3311132452718499</v>
       </c>
       <c r="G114">
-        <v>0.1144447648451781</v>
+        <v>0.1490354522040866</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C115">
-        <v>-0.09517727200902064</v>
+        <v>0.09085850858002754</v>
       </c>
       <c r="D115">
-        <v>0.4071634681838424</v>
+        <v>0.4288719785015935</v>
       </c>
       <c r="E115">
-        <v>0.4815150580261093</v>
+        <v>0.5073022084236998</v>
       </c>
       <c r="F115">
-        <v>-0.313416759713376</v>
+        <v>-0.1491940463125953</v>
       </c>
       <c r="G115">
-        <v>0.144811448234273</v>
+        <v>0.3139709995055478</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -3084,19 +3084,19 @@
         <v>8</v>
       </c>
       <c r="C116">
-        <v>0.09544284770822199</v>
+        <v>0.09083953558873176</v>
       </c>
       <c r="D116">
-        <v>0.4058498486723551</v>
+        <v>0.428968779181805</v>
       </c>
       <c r="E116">
-        <v>0.4815150580261093</v>
+        <v>0.5073022084236998</v>
       </c>
       <c r="F116">
-        <v>-0.1507935596491015</v>
+        <v>-0.1577517231859039</v>
       </c>
       <c r="G116">
-        <v>0.3342784284060647</v>
+        <v>0.3172364113319099</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -3104,137 +3104,137 @@
         <v>21</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C117">
-        <v>-0.08676737486764424</v>
+        <v>-0.08954959647832515</v>
       </c>
       <c r="D117">
-        <v>0.4500313393162855</v>
+        <v>0.4355792219116649</v>
       </c>
       <c r="E117">
-        <v>0.5276229495432312</v>
+        <v>0.5106790877585036</v>
       </c>
       <c r="F117">
-        <v>-0.2944914455926955</v>
+        <v>-0.2970392780053965</v>
       </c>
       <c r="G117">
-        <v>0.1240541828998844</v>
+        <v>0.1296591468780544</v>
       </c>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C118">
-        <v>-0.08313749941526964</v>
+        <v>0.08316999456239961</v>
       </c>
       <c r="D118">
-        <v>0.4692805613489612</v>
+        <v>0.4691062836659365</v>
       </c>
       <c r="E118">
-        <v>0.5454885157560575</v>
+        <v>0.545285936568952</v>
       </c>
       <c r="F118">
-        <v>-0.3151189525804879</v>
+        <v>-0.1689496994621955</v>
       </c>
       <c r="G118">
-        <v>0.1683475301322072</v>
+        <v>0.3083410070659157</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B119" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C119">
-        <v>-0.07932573755358563</v>
+        <v>-0.08162723352596768</v>
       </c>
       <c r="D119">
-        <v>0.4899653285034575</v>
+        <v>0.4774190007530238</v>
       </c>
       <c r="E119">
-        <v>0.5552940389705852</v>
+        <v>0.5502456279865359</v>
       </c>
       <c r="F119">
-        <v>-0.3101384890966463</v>
+        <v>-0.3085031760766038</v>
       </c>
       <c r="G119">
-        <v>0.1671806195272558</v>
+        <v>0.1404343813038232</v>
       </c>
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C120">
-        <v>-0.07980626967968739</v>
+        <v>0.07997595345034952</v>
       </c>
       <c r="D120">
-        <v>0.4873314906218922</v>
+        <v>0.4864032325965809</v>
       </c>
       <c r="E120">
-        <v>0.5552940389705852</v>
+        <v>0.5558894086818067</v>
       </c>
       <c r="F120">
-        <v>-0.3134313984463643</v>
+        <v>-0.1672371622759817</v>
       </c>
       <c r="G120">
-        <v>0.1574768906307482</v>
+        <v>0.3548821990852508</v>
       </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C121">
-        <v>-0.07971064914600812</v>
+        <v>0.07446983396350483</v>
       </c>
       <c r="D121">
-        <v>0.4878549971128565</v>
+        <v>0.5169967219051423</v>
       </c>
       <c r="E121">
-        <v>0.5552940389705852</v>
+        <v>0.5859296181591613</v>
       </c>
       <c r="F121">
-        <v>-0.2999744575577531</v>
+        <v>-0.1512418300975782</v>
       </c>
       <c r="G121">
-        <v>0.1389883289247196</v>
+        <v>0.2921230962185639</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C122">
-        <v>0.0777071030235587</v>
+        <v>-0.0720974791022358</v>
       </c>
       <c r="D122">
-        <v>0.4988921438644718</v>
+        <v>0.5304727789700616</v>
       </c>
       <c r="E122">
-        <v>0.5607382774013898</v>
+        <v>0.5962338672721353</v>
       </c>
       <c r="F122">
-        <v>-0.1655064519499754</v>
+        <v>-0.2978588902342485</v>
       </c>
       <c r="G122">
-        <v>0.2871691669153947</v>
+        <v>0.1596106140265338</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -3242,22 +3242,22 @@
         <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C123">
-        <v>0.07207804419161601</v>
+        <v>-0.06984155085420907</v>
       </c>
       <c r="D123">
-        <v>0.5305838955246727</v>
+        <v>0.5434475876914013</v>
       </c>
       <c r="E123">
-        <v>0.5786782449538179</v>
+        <v>0.6008851376100047</v>
       </c>
       <c r="F123">
-        <v>-0.1830842089595682</v>
+        <v>-0.3164851307581811</v>
       </c>
       <c r="G123">
-        <v>0.3239104728488644</v>
+        <v>0.1680805104224489</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -3265,45 +3265,45 @@
         <v>23</v>
       </c>
       <c r="B124" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C124">
-        <v>-0.07185265274522881</v>
+        <v>-0.07001858900593076</v>
       </c>
       <c r="D124">
-        <v>0.5318733869060827</v>
+        <v>0.5424237950072195</v>
       </c>
       <c r="E124">
-        <v>0.5786782449538179</v>
+        <v>0.6008851376100047</v>
       </c>
       <c r="F124">
-        <v>-0.3025872922996393</v>
+        <v>-0.2965415664748867</v>
       </c>
       <c r="G124">
-        <v>0.1767377217540674</v>
+        <v>0.1712147795789936</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C125">
-        <v>0.07232923326711869</v>
+        <v>-0.06566850870648337</v>
       </c>
       <c r="D125">
-        <v>0.5291486479049519</v>
+        <v>0.567849136278622</v>
       </c>
       <c r="E125">
-        <v>0.5786782449538179</v>
+        <v>0.6228022784991337</v>
       </c>
       <c r="F125">
-        <v>-0.1491895626649856</v>
+        <v>-0.2991762526713543</v>
       </c>
       <c r="G125">
-        <v>0.2980760828969653</v>
+        <v>0.1676667274401266</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -3311,91 +3311,91 @@
         <v>23</v>
       </c>
       <c r="B126" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C126">
-        <v>0.07317998457238961</v>
+        <v>-0.05935873846992328</v>
       </c>
       <c r="D126">
-        <v>0.5243020387227605</v>
+        <v>0.6056911227551218</v>
       </c>
       <c r="E126">
-        <v>0.5786782449538179</v>
+        <v>0.6589919415575726</v>
       </c>
       <c r="F126">
-        <v>-0.140653553474027</v>
+        <v>-0.2733480201642348</v>
       </c>
       <c r="G126">
-        <v>0.2976990478764048</v>
+        <v>0.1738281377204846</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C127">
-        <v>-0.0485463903185422</v>
+        <v>0.05084686631743222</v>
       </c>
       <c r="D127">
-        <v>0.672968879909476</v>
+        <v>0.6584144618542884</v>
       </c>
       <c r="E127">
-        <v>0.72637910847372</v>
+        <v>0.71066957787447</v>
       </c>
       <c r="F127">
-        <v>-0.2721820463277573</v>
+        <v>-0.1834678405254865</v>
       </c>
       <c r="G127">
-        <v>0.1732380141945513</v>
+        <v>0.2678609188298182</v>
       </c>
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C128">
-        <v>0.03985912732364683</v>
+        <v>0.04224889035015617</v>
       </c>
       <c r="D128">
-        <v>0.7289816204005031</v>
+        <v>0.7134162115503071</v>
       </c>
       <c r="E128">
-        <v>0.7806417352320348</v>
+        <v>0.76397326591214</v>
       </c>
       <c r="F128">
-        <v>-0.2071873521661151</v>
+        <v>-0.2102459552663825</v>
       </c>
       <c r="G128">
-        <v>0.2860241390148202</v>
+        <v>0.2710611480379665</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C129">
-        <v>0.03885987430291227</v>
+        <v>0.04082019765251648</v>
       </c>
       <c r="D129">
-        <v>0.7355231576771569</v>
+        <v>0.7227082295179067</v>
       </c>
       <c r="E129">
-        <v>0.7814933550319793</v>
+        <v>0.7678774938627758</v>
       </c>
       <c r="F129">
-        <v>-0.2022170686291214</v>
+        <v>-0.2061681108555629</v>
       </c>
       <c r="G129">
-        <v>0.2752612848234703</v>
+        <v>0.2978265546303561</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -3406,19 +3406,19 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.03481328797784494</v>
+        <v>0.03691245463397361</v>
       </c>
       <c r="D130">
-        <v>0.7622020667074854</v>
+        <v>0.7483255770275212</v>
       </c>
       <c r="E130">
-        <v>0.8035618687768838</v>
+        <v>0.7889323912848286</v>
       </c>
       <c r="F130">
-        <v>-0.2237770012238711</v>
+        <v>-0.2209058394562374</v>
       </c>
       <c r="G130">
-        <v>0.2696492537710996</v>
+        <v>0.2887976313767203</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -3429,42 +3429,42 @@
         <v>15</v>
       </c>
       <c r="C131">
-        <v>0.03190480405670278</v>
+        <v>0.03473741448424992</v>
       </c>
       <c r="D131">
-        <v>0.7815521435460968</v>
+        <v>0.7627050622023136</v>
       </c>
       <c r="E131">
-        <v>0.8176237809405321</v>
+        <v>0.7979068343039589</v>
       </c>
       <c r="F131">
-        <v>-0.2223741981636376</v>
+        <v>-0.2041196002829331</v>
       </c>
       <c r="G131">
-        <v>0.282410763483751</v>
+        <v>0.2768957879252528</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B132" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C132">
-        <v>-0.02879399081930727</v>
+        <v>-0.02978034623604243</v>
       </c>
       <c r="D132">
-        <v>0.8023957312114622</v>
+        <v>0.7957711002762243</v>
       </c>
       <c r="E132">
-        <v>0.8330215224790752</v>
+        <v>0.8261440430348588</v>
       </c>
       <c r="F132">
-        <v>-0.2647024870151282</v>
+        <v>-0.2601126973018283</v>
       </c>
       <c r="G132">
-        <v>0.1968325298763975</v>
+        <v>0.1989650688790731</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3475,88 +3475,88 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>-0.02247119968638956</v>
+        <v>-0.02161130009231274</v>
       </c>
       <c r="D133">
-        <v>0.845173180814582</v>
+        <v>0.8510285819387664</v>
       </c>
       <c r="E133">
-        <v>0.8702069465775815</v>
+        <v>0.8768173268460018</v>
       </c>
       <c r="F133">
-        <v>-0.2532159373101197</v>
+        <v>-0.2552222426198495</v>
       </c>
       <c r="G133">
-        <v>0.2045904257594782</v>
+        <v>0.2095842376676867</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B134" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C134">
-        <v>0.02107344138691047</v>
+        <v>0.01093842865994765</v>
       </c>
       <c r="D134">
-        <v>0.8546951953955688</v>
+        <v>0.924276144944562</v>
       </c>
       <c r="E134">
-        <v>0.8702069465775815</v>
+        <v>0.9451244790410558</v>
       </c>
       <c r="F134">
-        <v>-0.1986443339875502</v>
+        <v>-0.2294013296486803</v>
       </c>
       <c r="G134">
-        <v>0.247882872595495</v>
+        <v>0.2672320987896402</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B135" t="s">
         <v>20</v>
       </c>
       <c r="C135">
-        <v>0.02067552700464092</v>
+        <v>-0.003856902591079805</v>
       </c>
       <c r="D135">
-        <v>0.8574097855984993</v>
+        <v>0.9732651780591355</v>
       </c>
       <c r="E135">
-        <v>0.8702069465775815</v>
+        <v>0.9786983704180139</v>
       </c>
       <c r="F135">
-        <v>-0.2178283121312366</v>
+        <v>-0.2387559939670751</v>
       </c>
       <c r="G135">
-        <v>0.2666633077096758</v>
+        <v>0.2446171996257264</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B136" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C136">
-        <v>0.006133107398930183</v>
+        <v>-0.004049750414662743</v>
       </c>
       <c r="D136">
-        <v>0.9574991685492527</v>
+        <v>0.9719289461102606</v>
       </c>
       <c r="E136">
-        <v>0.9645917549829507</v>
+        <v>0.9786983704180139</v>
       </c>
       <c r="F136">
-        <v>-0.232781219891867</v>
+        <v>-0.2257842975028577</v>
       </c>
       <c r="G136">
-        <v>0.2341143352095647</v>
+        <v>0.2114665169876459</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -3567,19 +3567,19 @@
         <v>20</v>
       </c>
       <c r="C137">
-        <v>0.00312345881966135</v>
+        <v>-0.003072876490598009</v>
       </c>
       <c r="D137">
-        <v>0.9783478100005689</v>
+        <v>0.9786983704180139</v>
       </c>
       <c r="E137">
-        <v>0.9783478100005689</v>
+        <v>0.9786983704180139</v>
       </c>
       <c r="F137">
-        <v>-0.2201499582777407</v>
+        <v>-0.2256337924791574</v>
       </c>
       <c r="G137">
-        <v>0.2399464411992127</v>
+        <v>0.2312211178637894</v>
       </c>
     </row>
   </sheetData>
